--- a/stories/arbres/TREE-JEU-008.xlsx
+++ b/stories/arbres/TREE-JEU-008.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nora est près de la fenêtre avec maman. Dans la cour, un petit jeu de foot. On vise le but. On se passe le ballon. On reste dans l'espace montré. Papa est déjà dans la cour.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Une feuille tombe. Dans la cour, Nora vise le but. Elle se passe le ballon. Elle reste dans l'espace montré. Maman montre le rectangle.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1857,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Petit jeu de foot. Nora fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2030,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. But. Passer. Espace montré. On continue avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2221,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2388,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a le ballon rouge. Le soleil chauffe un peu. Si c'est le ballon, on le passe. On vise le but. Dans l'espace montré. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2581,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2750,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. Ça sent l'herbe coupée. Nora se passe le ballon avec Tom. On vise le but. Dans l'espace montré. Le ballon rouge reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2917,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3084,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa. Le soleil chauffe un peu. Nora se passe le ballon avec Léa. On vise le but. Dans l'espace montré. Le ballon rouge reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3251,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3418,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. Le sol est frais. Nora se passe le ballon avec Sami. On vise le but. Dans l'espace montré. Le ballon rouge reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3585,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3752,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a le seau bleu. Le sol est frais. Si c'est le ballon, on le passe. On vise le but. Dans l'espace montré. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3945,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4114,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. Le soleil chauffe un peu. Nora se passe le ballon avec Tom. On vise le but. Dans l'espace montré. Le seau bleu reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4281,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4448,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa. Le sol est frais. Nora se passe le ballon avec Léa. On vise le but. Dans l'espace montré. Le seau bleu reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4615,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4782,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. Un petit bruit d'eau. Nora se passe le ballon avec Sami. On vise le but. Dans l'espace montré. Le seau bleu reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4949,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5116,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a le doudou. Un petit bruit d'eau. Si c'est le ballon, on le passe. On vise le but. Dans l'espace montré. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5309,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5478,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. Le sol est frais. Nora se passe le ballon avec Tom. On vise le but. Dans l'espace montré. Le doudou reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5645,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5812,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa. Un petit bruit d'eau. Nora se passe le ballon avec Léa. On vise le but. Dans l'espace montré. Le doudou reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5979,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6146,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. Les chaussures font toc toc. Nora se passe le ballon avec Sami. On vise le but. Dans l'espace montré. Le doudou reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6313,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6313,6 +6480,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le vent est doux. Dans la cour, Nora vise le but. Elle se passe le ballon. Elle reste dans l'espace montré. Maman montre le rectangle.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6661,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Petit jeu de foot. Nora fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6834,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. But. Passer. Espace montré. On continue avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7025,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7192,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a le ballon rouge. Le soleil chauffe un peu. Si c'est le ballon, on le passe. On vise le but. Dans l'espace montré. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7193,6 +7385,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7357,6 +7554,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. Le soleil chauffe un peu. Nora se passe le ballon avec Tom. On vise le but. Dans l'espace montré. Le ballon rouge reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7721,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7888,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa. Le sol est frais. Nora se passe le ballon avec Léa. On vise le but. Dans l'espace montré. Le ballon rouge reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8055,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8222,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. Un petit bruit d'eau. Nora se passe le ballon avec Sami. On vise le but. Dans l'espace montré. Le ballon rouge reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8389,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8556,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a le seau bleu. Le sol est frais. Si c'est le ballon, on le passe. On vise le but. Dans l'espace montré. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8517,6 +8749,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8681,6 +8918,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. Le sol est frais. Nora se passe le ballon avec Tom. On vise le but. Dans l'espace montré. Le seau bleu reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9085,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9252,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa. Un petit bruit d'eau. Nora se passe le ballon avec Léa. On vise le but. Dans l'espace montré. Le seau bleu reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9419,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9586,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. Les chaussures font toc toc. Nora se passe le ballon avec Sami. On vise le but. Dans l'espace montré. Le seau bleu reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9753,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9920,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a le doudou. Un petit bruit d'eau. Si c'est le ballon, on le passe. On vise le but. Dans l'espace montré. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9841,6 +10113,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10005,6 +10282,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. Un petit bruit d'eau. Nora se passe le ballon avec Tom. On vise le but. Dans l'espace montré. Le doudou reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10449,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10616,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa. Les chaussures font toc toc. Nora se passe le ballon avec Léa. On vise le but. Dans l'espace montré. Le doudou reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10783,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10950,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. Un vélo passe au loin. Nora se passe le ballon avec Sami. On vise le but. Dans l'espace montré. Le doudou reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11117,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10977,6 +11284,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. On entend un oiseau. Dans la cour, Nora vise le but. Elle se passe le ballon. Elle reste dans l'espace montré. Maman montre le rectangle.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11465,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Petit jeu de foot. Nora fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11638,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. But. Passer. Espace montré. On continue avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11829,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11669,6 +11996,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a le ballon rouge. Le soleil chauffe un peu. Si c'est le ballon, on le passe. On vise le but. Dans l'espace montré. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11857,6 +12189,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12021,6 +12358,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. Le sol est frais. Nora se passe le ballon avec Tom. On vise le but. Dans l'espace montré. Le ballon rouge reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12525,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12692,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa. Un petit bruit d'eau. Nora se passe le ballon avec Léa. On vise le but. Dans l'espace montré. Le ballon rouge reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12859,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13026,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. Les chaussures font toc toc. Nora se passe le ballon avec Sami. On vise le but. Dans l'espace montré. Le ballon rouge reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13193,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13360,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a le seau bleu. Le sol est frais. Si c'est le ballon, on le passe. On vise le but. Dans l'espace montré. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13181,6 +13553,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13345,6 +13722,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. Un petit bruit d'eau. Nora se passe le ballon avec Tom. On vise le but. Dans l'espace montré. Le seau bleu reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13889,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14056,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa. Les chaussures font toc toc. Nora se passe le ballon avec Léa. On vise le but. Dans l'espace montré. Le seau bleu reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14223,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13993,6 +14390,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. Un vélo passe au loin. Nora se passe le ballon avec Sami. On vise le but. Dans l'espace montré. Le seau bleu reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14557,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14724,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a le doudou. Un petit bruit d'eau. Si c'est le ballon, on le passe. On vise le but. Dans l'espace montré. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14505,6 +14917,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14669,6 +15086,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. Les chaussures font toc toc. Nora se passe le ballon avec Tom. On vise le but. Dans l'espace montré. Le doudou reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15253,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15420,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa. Un vélo passe au loin. Nora se passe le ballon avec Léa. On vise le but. Dans l'espace montré. Le doudou reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15587,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15317,6 +15754,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. La lumière est claire. Nora se passe le ballon avec Sami. On vise le but. Dans l'espace montré. Le doudou reste au bord. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15921,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16017,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-JEU-008.xlsx
+++ b/stories/arbres/TREE-JEU-008.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Nora est près de la fenêtre avec maman. Dans la cour, un petit jeu de foot. On vise le but. On se passe le ballon. On reste dans l'espace montré. Papa est déjà dans la cour.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1688,7 @@
           <t>narrateur|C'est le matin. Une feuille tombe. Dans la cour, Nora vise le but. Elle se passe le ballon. Elle reste dans l'espace montré. Maman montre le rectangle.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1864,6 +1872,7 @@
           <t>narrateur|Petit jeu de foot. Nora fait quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2035,6 +2044,7 @@
           <t>narrateur|Oui. But. Passer. Espace montré. On continue avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2226,6 +2236,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2393,6 +2404,7 @@
           <t>narrateur|Nora a le ballon rouge. Le soleil chauffe un peu. Si c'est le ballon, on le passe. On vise le but. Dans l'espace montré. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2588,6 +2600,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2755,6 +2768,7 @@
           <t>narrateur|Nora rejoint Tom. Ça sent l'herbe coupée. Nora se passe le ballon avec Tom. On vise le but. Dans l'espace montré. Le ballon rouge reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2922,6 +2936,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3089,6 +3104,7 @@
           <t>narrateur|Nora rejoint Léa. Le soleil chauffe un peu. Nora se passe le ballon avec Léa. On vise le but. Dans l'espace montré. Le ballon rouge reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3256,6 +3272,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3423,6 +3440,7 @@
           <t>narrateur|Nora rejoint Sami. Le sol est frais. Nora se passe le ballon avec Sami. On vise le but. Dans l'espace montré. Le ballon rouge reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3590,6 +3608,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3757,6 +3776,7 @@
           <t>narrateur|Nora a le seau bleu. Le sol est frais. Si c'est le ballon, on le passe. On vise le but. Dans l'espace montré. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3952,6 +3972,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4119,6 +4140,7 @@
           <t>narrateur|Nora rejoint Tom. Le soleil chauffe un peu. Nora se passe le ballon avec Tom. On vise le but. Dans l'espace montré. Le seau bleu reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4286,6 +4308,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4453,6 +4476,7 @@
           <t>narrateur|Nora rejoint Léa. Le sol est frais. Nora se passe le ballon avec Léa. On vise le but. Dans l'espace montré. Le seau bleu reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4620,6 +4644,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4787,6 +4812,7 @@
           <t>narrateur|Nora rejoint Sami. Un petit bruit d'eau. Nora se passe le ballon avec Sami. On vise le but. Dans l'espace montré. Le seau bleu reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4954,6 +4980,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5121,6 +5148,7 @@
           <t>narrateur|Nora a le doudou. Un petit bruit d'eau. Si c'est le ballon, on le passe. On vise le but. Dans l'espace montré. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5316,6 +5344,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5483,6 +5512,7 @@
           <t>narrateur|Nora rejoint Tom. Le sol est frais. Nora se passe le ballon avec Tom. On vise le but. Dans l'espace montré. Le doudou reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5650,6 +5680,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5817,6 +5848,7 @@
           <t>narrateur|Nora rejoint Léa. Un petit bruit d'eau. Nora se passe le ballon avec Léa. On vise le but. Dans l'espace montré. Le doudou reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5984,6 +6016,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6151,6 +6184,7 @@
           <t>narrateur|Nora rejoint Sami. Les chaussures font toc toc. Nora se passe le ballon avec Sami. On vise le but. Dans l'espace montré. Le doudou reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6318,6 +6352,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6485,6 +6520,7 @@
           <t>narrateur|C'est après la sieste. Le vent est doux. Dans la cour, Nora vise le but. Elle se passe le ballon. Elle reste dans l'espace montré. Maman montre le rectangle.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6668,6 +6704,7 @@
           <t>narrateur|Petit jeu de foot. Nora fait quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6839,6 +6876,7 @@
           <t>narrateur|Oui. But. Passer. Espace montré. On continue avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7030,6 +7068,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7197,6 +7236,7 @@
           <t>narrateur|Nora a le ballon rouge. Le soleil chauffe un peu. Si c'est le ballon, on le passe. On vise le but. Dans l'espace montré. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7392,6 +7432,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7559,6 +7600,7 @@
           <t>narrateur|Nora rejoint Tom. Le soleil chauffe un peu. Nora se passe le ballon avec Tom. On vise le but. Dans l'espace montré. Le ballon rouge reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7726,6 +7768,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7893,6 +7936,7 @@
           <t>narrateur|Nora rejoint Léa. Le sol est frais. Nora se passe le ballon avec Léa. On vise le but. Dans l'espace montré. Le ballon rouge reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8060,6 +8104,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8227,6 +8272,7 @@
           <t>narrateur|Nora rejoint Sami. Un petit bruit d'eau. Nora se passe le ballon avec Sami. On vise le but. Dans l'espace montré. Le ballon rouge reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8394,6 +8440,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8561,6 +8608,7 @@
           <t>narrateur|Nora a le seau bleu. Le sol est frais. Si c'est le ballon, on le passe. On vise le but. Dans l'espace montré. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8756,6 +8804,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8923,6 +8972,7 @@
           <t>narrateur|Nora rejoint Tom. Le sol est frais. Nora se passe le ballon avec Tom. On vise le but. Dans l'espace montré. Le seau bleu reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9090,6 +9140,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9257,6 +9308,7 @@
           <t>narrateur|Nora rejoint Léa. Un petit bruit d'eau. Nora se passe le ballon avec Léa. On vise le but. Dans l'espace montré. Le seau bleu reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9424,6 +9476,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9591,6 +9644,7 @@
           <t>narrateur|Nora rejoint Sami. Les chaussures font toc toc. Nora se passe le ballon avec Sami. On vise le but. Dans l'espace montré. Le seau bleu reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9758,6 +9812,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9925,6 +9980,7 @@
           <t>narrateur|Nora a le doudou. Un petit bruit d'eau. Si c'est le ballon, on le passe. On vise le but. Dans l'espace montré. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10120,6 +10176,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10287,6 +10344,7 @@
           <t>narrateur|Nora rejoint Tom. Un petit bruit d'eau. Nora se passe le ballon avec Tom. On vise le but. Dans l'espace montré. Le doudou reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10454,6 +10512,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10621,6 +10680,7 @@
           <t>narrateur|Nora rejoint Léa. Les chaussures font toc toc. Nora se passe le ballon avec Léa. On vise le but. Dans l'espace montré. Le doudou reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10788,6 +10848,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10955,6 +11016,7 @@
           <t>narrateur|Nora rejoint Sami. Un vélo passe au loin. Nora se passe le ballon avec Sami. On vise le but. Dans l'espace montré. Le doudou reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11122,6 +11184,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11289,6 +11352,7 @@
           <t>narrateur|C'est le soir. On entend un oiseau. Dans la cour, Nora vise le but. Elle se passe le ballon. Elle reste dans l'espace montré. Maman montre le rectangle.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11472,6 +11536,7 @@
           <t>narrateur|Petit jeu de foot. Nora fait quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11643,6 +11708,7 @@
           <t>narrateur|Oui. But. Passer. Espace montré. On continue avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11834,6 +11900,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12001,6 +12068,7 @@
           <t>narrateur|Nora a le ballon rouge. Le soleil chauffe un peu. Si c'est le ballon, on le passe. On vise le but. Dans l'espace montré. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12196,6 +12264,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12363,6 +12432,7 @@
           <t>narrateur|Nora rejoint Tom. Le sol est frais. Nora se passe le ballon avec Tom. On vise le but. Dans l'espace montré. Le ballon rouge reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12530,6 +12600,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12697,6 +12768,7 @@
           <t>narrateur|Nora rejoint Léa. Un petit bruit d'eau. Nora se passe le ballon avec Léa. On vise le but. Dans l'espace montré. Le ballon rouge reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12864,6 +12936,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13031,6 +13104,7 @@
           <t>narrateur|Nora rejoint Sami. Les chaussures font toc toc. Nora se passe le ballon avec Sami. On vise le but. Dans l'espace montré. Le ballon rouge reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13198,6 +13272,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13365,6 +13440,7 @@
           <t>narrateur|Nora a le seau bleu. Le sol est frais. Si c'est le ballon, on le passe. On vise le but. Dans l'espace montré. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13560,6 +13636,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13727,6 +13804,7 @@
           <t>narrateur|Nora rejoint Tom. Un petit bruit d'eau. Nora se passe le ballon avec Tom. On vise le but. Dans l'espace montré. Le seau bleu reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13894,6 +13972,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14061,6 +14140,7 @@
           <t>narrateur|Nora rejoint Léa. Les chaussures font toc toc. Nora se passe le ballon avec Léa. On vise le but. Dans l'espace montré. Le seau bleu reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14228,6 +14308,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14395,6 +14476,7 @@
           <t>narrateur|Nora rejoint Sami. Un vélo passe au loin. Nora se passe le ballon avec Sami. On vise le but. Dans l'espace montré. Le seau bleu reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14562,6 +14644,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14729,6 +14812,7 @@
           <t>narrateur|Nora a le doudou. Un petit bruit d'eau. Si c'est le ballon, on le passe. On vise le but. Dans l'espace montré. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14924,6 +15008,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15091,6 +15176,7 @@
           <t>narrateur|Nora rejoint Tom. Les chaussures font toc toc. Nora se passe le ballon avec Tom. On vise le but. Dans l'espace montré. Le doudou reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15258,6 +15344,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15425,6 +15512,7 @@
           <t>narrateur|Nora rejoint Léa. Un vélo passe au loin. Nora se passe le ballon avec Léa. On vise le but. Dans l'espace montré. Le doudou reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15592,6 +15680,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15759,6 +15848,7 @@
           <t>narrateur|Nora rejoint Sami. La lumière est claire. Nora se passe le ballon avec Sami. On vise le but. Dans l'espace montré. Le doudou reste au bord. Merci maman.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15926,6 +16016,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15944,7 +16035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16024,6 +16115,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16038,7 +16143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16225,6 +16330,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
